--- a/kits/security-questionnaire/samples/output/cobalt-ridge-supplier-security-questionnaire_DRAFT2.xlsx
+++ b/kits/security-questionnaire/samples/output/cobalt-ridge-supplier-security-questionnaire_DRAFT2.xlsx
@@ -2425,7 +2425,7 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>coverag, cyber, limit, cyberinsurance, insur</t>
+          <t>coverag, cyber, cyberinsurance, limit, insur</t>
         </is>
       </c>
       <c r="P8" s="17" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>idp, ident, customeruser, provid, login</t>
+          <t>ident, idp, customeruser, provid, login</t>
         </is>
       </c>
       <c r="P9" s="17" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>web, waf, ddos, firewal, applic, protect</t>
+          <t>web, ddos, firewal, waf, applic, protect</t>
         </is>
       </c>
       <c r="P11" s="17" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>endpoint, anti, malwar, antimalware, detect, softwar</t>
+          <t>anti, endpoint, malwar, antimalware, detect, softwar</t>
         </is>
       </c>
       <c r="P12" s="17" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>certif, 27001, iso27001, iso, hold</t>
+          <t>certif, 27001, hold, iso, iso27001</t>
         </is>
       </c>
       <c r="P15" s="17" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>backgroundcheck, background, check</t>
+          <t>background, backgroundcheck, check</t>
         </is>
       </c>
       <c r="P17" s="17" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>sever, fix, vulner, timeframe</t>
+          <t>fix, sever, vulner, timeframe</t>
         </is>
       </c>
       <c r="P25" s="17" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>autom, static, analys, depscan, sast, depend</t>
+          <t>analys, autom, depscan, static, sast, depend</t>
         </is>
       </c>
       <c r="P42" s="17" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>region, outage</t>
+          <t>outage, region</t>
         </is>
       </c>
       <c r="P46" s="17" t="inlineStr">
